--- a/artfynd/S 150-2022 artfynd.xlsx
+++ b/artfynd/S 150-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY67"/>
+  <dimension ref="A1:AZ67"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -785,6 +790,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/16612341</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -898,6 +908,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/16612539</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1011,6 +1026,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/16612578</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1124,6 +1144,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/55136542</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1237,6 +1262,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/55136556</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1350,6 +1380,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/55136655</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1458,6 +1493,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/16623123</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1566,6 +1606,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/16623124</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1674,6 +1719,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/16623144</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1787,6 +1837,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/16866280</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1900,6 +1955,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/16936136</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -2013,6 +2073,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/16936251</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2126,6 +2191,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/16936514</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2239,6 +2309,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/17183000</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2347,6 +2422,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/17183065</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2460,6 +2540,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/56208760</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2573,6 +2658,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/57193572</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2686,6 +2776,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/57193588</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2799,6 +2894,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/57193601</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2912,6 +3012,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/57193610</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -3025,6 +3130,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/57193624</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -3138,6 +3248,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/57755403</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3251,6 +3366,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/57755425</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3364,6 +3484,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/57755441</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3477,6 +3602,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/57755451</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3590,6 +3720,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/57755461</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3698,6 +3833,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/57810487</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3811,6 +3951,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/71202448</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3924,6 +4069,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/71202484</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -4037,6 +4187,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/71202505</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -4150,6 +4305,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/71202511</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -4263,6 +4423,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/71202536</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -4371,6 +4536,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/71202727</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4479,6 +4649,11 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/71202894</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4593,6 +4768,11 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/76382968</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4702,6 +4882,11 @@
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/83059744</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4808,6 +4993,11 @@
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/92383883</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -4921,6 +5111,11 @@
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/16612124</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -5034,6 +5229,11 @@
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/16612366</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -5147,6 +5347,11 @@
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/16623125</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -5260,6 +5465,11 @@
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/16936343</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -5373,6 +5583,11 @@
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/57193617</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -5486,6 +5701,11 @@
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/16612590</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -5593,6 +5813,11 @@
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/95884759</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -5701,6 +5926,11 @@
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/55136735</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -5809,6 +6039,11 @@
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/16611902</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -5909,6 +6144,11 @@
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
+      <c r="AZ48" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/55136485</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -6009,6 +6249,11 @@
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
+      <c r="AZ49" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/55136755</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -6110,6 +6355,11 @@
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
+      <c r="AZ50" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/88405507</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -6219,6 +6469,11 @@
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
+      <c r="AZ51" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/95884874</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -6327,6 +6582,11 @@
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
+      <c r="AZ52" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/16936027</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -6434,6 +6694,11 @@
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
+      <c r="AZ53" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/17183006</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -6546,6 +6811,11 @@
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
+      <c r="AZ54" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/88405435</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -6653,6 +6923,11 @@
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
+      <c r="AZ55" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/16611911</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -6755,6 +7030,11 @@
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
+      <c r="AZ56" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/91833303</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
@@ -6862,6 +7142,11 @@
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
+      <c r="AZ57" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/95390616</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
@@ -6975,6 +7260,11 @@
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
+      <c r="AZ58" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/16612106</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
@@ -7088,6 +7378,11 @@
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
+      <c r="AZ59" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/16612363</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
@@ -7201,6 +7496,11 @@
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
+      <c r="AZ60" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/16612367</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
@@ -7301,6 +7601,11 @@
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
+      <c r="AZ61" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/71202698</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
@@ -7411,6 +7716,11 @@
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
+      <c r="AZ62" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/88405504</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
@@ -7517,6 +7827,11 @@
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
+      <c r="AZ63" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/91833304</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
@@ -7632,6 +7947,11 @@
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
+      <c r="AZ64" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/92778357</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
@@ -7739,6 +8059,11 @@
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
+      <c r="AZ65" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/95884814</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
@@ -7852,6 +8177,11 @@
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
+      <c r="AZ66" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/16612569</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
@@ -7965,8 +8295,81 @@
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
+      <c r="AZ67" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/16612585</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ50" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ51" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ52" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ53" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ54" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ55" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ56" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ57" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ58" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ59" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ60" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ61" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ62" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ63" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ64" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ65" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ66" r:id="rId65"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ67" r:id="rId66"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>